--- a/faturados.xlsx
+++ b/faturados.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malgarci\Documents\Mapfre_3\10 - AMA\ItensOrganiza\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GBASSI\Documents\Python\.vscode\SendMails\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EAB750-0FA9-4EF0-A766-9D6ECC896DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CACBA3-892A-43FD-8437-C82EEEAFA970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mesclado" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Mesclado!$A$1:$H$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$F$65</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="125">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -408,13 +410,19 @@
   </si>
   <si>
     <t>VATICANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDADOS </t>
+  </si>
+  <si>
+    <t>PENDENTE EXECUÇÃO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,6 +434,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -843,22 +852,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K65"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.5703125" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" customWidth="1"/>
-    <col min="4" max="4" width="33.42578125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="31.140625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="44.28515625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="25.42578125" customWidth="1"/>
-    <col min="9" max="9" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5546875" customWidth="1"/>
+    <col min="3" max="3" width="25.109375" customWidth="1"/>
+    <col min="4" max="4" width="33.44140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="31.109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="44.33203125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="25.44140625" customWidth="1"/>
+    <col min="9" max="9" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -893,7 +902,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -916,7 +925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -942,7 +951,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -968,7 +977,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -997,7 +1006,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1026,7 +1035,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1055,7 +1064,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -1081,7 +1090,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -1110,7 +1119,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -1136,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -1162,7 +1171,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1188,7 +1197,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1214,7 +1223,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1240,7 +1249,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1266,7 +1275,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1292,7 +1301,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1318,7 +1327,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1344,7 +1353,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1376,7 +1385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -1402,7 +1411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1431,7 +1440,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1457,7 +1466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1480,7 +1489,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1506,7 +1515,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1532,7 +1541,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -1561,7 +1570,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1587,7 +1596,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1613,7 +1622,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -1639,7 +1648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -1665,7 +1674,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -1691,7 +1700,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>75</v>
       </c>
@@ -1717,7 +1726,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1743,7 +1752,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1772,7 +1781,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -1804,7 +1813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>83</v>
       </c>
@@ -1833,7 +1842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -1859,7 +1868,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>87</v>
       </c>
@@ -1885,7 +1894,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -1914,7 +1923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>92</v>
       </c>
@@ -1940,7 +1949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>94</v>
       </c>
@@ -1969,7 +1978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>95</v>
       </c>
@@ -1995,7 +2004,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -2021,7 +2030,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>97</v>
       </c>
@@ -2050,7 +2059,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -2076,7 +2085,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>99</v>
       </c>
@@ -2102,7 +2111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>100</v>
       </c>
@@ -2131,7 +2140,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>102</v>
       </c>
@@ -2157,7 +2166,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>103</v>
       </c>
@@ -2183,7 +2192,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -2209,7 +2218,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -2238,7 +2247,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>107</v>
       </c>
@@ -2264,7 +2273,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>108</v>
       </c>
@@ -2290,7 +2299,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>109</v>
       </c>
@@ -2316,7 +2325,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>110</v>
       </c>
@@ -2342,7 +2351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>111</v>
       </c>
@@ -2371,7 +2380,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>112</v>
       </c>
@@ -2397,7 +2406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>114</v>
       </c>
@@ -2423,7 +2432,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>115</v>
       </c>
@@ -2452,7 +2461,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>116</v>
       </c>
@@ -2478,7 +2487,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>118</v>
       </c>
@@ -2504,7 +2513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>119</v>
       </c>
@@ -2530,7 +2539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>120</v>
       </c>
@@ -2559,7 +2568,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>121</v>
       </c>
@@ -2585,7 +2594,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>122</v>
       </c>
@@ -2625,6 +2634,1146 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FBAD3CA-6927-469A-8916-C1332B7D02EF}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F65"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>103</v>
+      </c>
+      <c r="B49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>104</v>
+      </c>
+      <c r="B50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>105</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" t="s">
+        <v>20</v>
+      </c>
+      <c r="F51" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>108</v>
+      </c>
+      <c r="B53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>109</v>
+      </c>
+      <c r="B54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" t="s">
+        <v>20</v>
+      </c>
+      <c r="F55" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" t="s">
+        <v>20</v>
+      </c>
+      <c r="F57" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" t="s">
+        <v>20</v>
+      </c>
+      <c r="F58" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" t="s">
+        <v>20</v>
+      </c>
+      <c r="F59" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" t="s">
+        <v>20</v>
+      </c>
+      <c r="F60" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>119</v>
+      </c>
+      <c r="B62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>120</v>
+      </c>
+      <c r="B63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>121</v>
+      </c>
+      <c r="B64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>122</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" t="s">
+        <v>20</v>
+      </c>
+      <c r="F65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F65" xr:uid="{7FBAD3CA-6927-469A-8916-C1332B7D02EF}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="SIM"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{09b0f87a-e31e-4151-841c-33ff022e129b}" enabled="1" method="Standard" siteId="{5cc6c66d-ffb2-469f-9385-cda840e57836}" contentBits="2" removed="0"/>
